--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.07965278764315</v>
+        <v>3.587943577992012</v>
       </c>
       <c r="D2" t="n">
-        <v>22.07791869539547</v>
+        <v>3.587661788001764</v>
       </c>
       <c r="E2" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F2" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.37199177286224</v>
+        <v>5.422948663090115</v>
       </c>
       <c r="D3" t="n">
-        <v>34.16082333764237</v>
+        <v>5.551133792366885</v>
       </c>
       <c r="E3" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F3" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.77700403431236</v>
+        <v>4.513763155575758</v>
       </c>
       <c r="D4" t="n">
-        <v>28.6555350610416</v>
+        <v>4.65652444741926</v>
       </c>
       <c r="E4" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F4" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.93436290491981</v>
+        <v>2.10183397204947</v>
       </c>
       <c r="D5" t="n">
-        <v>12.94576874270654</v>
+        <v>2.103687420689812</v>
       </c>
       <c r="E5" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F5" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.64016658997573</v>
+        <v>3.516527070871057</v>
       </c>
       <c r="D6" t="n">
-        <v>22.44589595061897</v>
+        <v>3.647458091975583</v>
       </c>
       <c r="E6" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F6" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.20012252057117</v>
+        <v>3.282519909592815</v>
       </c>
       <c r="D7" t="n">
-        <v>20.61553786059453</v>
+        <v>3.350024902346612</v>
       </c>
       <c r="E7" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F7" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.41730431689855</v>
+        <v>2.180311951496014</v>
       </c>
       <c r="D8" t="n">
-        <v>13.24109061349962</v>
+        <v>2.151677224693687</v>
       </c>
       <c r="E8" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F8" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.95602292187002</v>
+        <v>2.430353724803878</v>
       </c>
       <c r="D9" t="n">
-        <v>14.60181509351396</v>
+        <v>2.372794952696018</v>
       </c>
       <c r="E9" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F9" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.35806439111839</v>
+        <v>4.445685463556739</v>
       </c>
       <c r="D10" t="n">
-        <v>26.52344972262016</v>
+        <v>4.310060579925776</v>
       </c>
       <c r="E10" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F10" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.43772991490429</v>
+        <v>2.508631111171947</v>
       </c>
       <c r="D11" t="n">
-        <v>15.44772620190504</v>
+        <v>2.510255507809569</v>
       </c>
       <c r="E11" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F11" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>19.04434162511692</v>
+        <v>3.094705514081499</v>
       </c>
       <c r="D12" t="n">
-        <v>19.03632917662976</v>
+        <v>3.093403491202336</v>
       </c>
       <c r="E12" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F12" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>29.00497148357767</v>
+        <v>4.713307866081372</v>
       </c>
       <c r="D13" t="n">
-        <v>28.99169925240163</v>
+        <v>4.711151128515266</v>
       </c>
       <c r="E13" t="n">
-        <v>6.437432559463262</v>
+        <v>1.04608279091278</v>
       </c>
       <c r="F13" t="n">
-        <v>6.623775002605726</v>
+        <v>1.076363437923431</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
